--- a/data/gold/results/01_eriksen_replication/table_s5_dk.xlsx
+++ b/data/gold/results/01_eriksen_replication/table_s5_dk.xlsx
@@ -388,13 +388,13 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>4864.111305166502</v>
+        <v>4608.260597065414</v>
       </c>
       <c r="C2">
-        <v>64720.67119886602</v>
+        <v>76453.5848395347</v>
       </c>
       <c r="D2">
-        <v>7.515545211545531</v>
+        <v>6.027527167937912</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -402,13 +402,13 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>5595.226019299745</v>
+        <v>4261.281022540152</v>
       </c>
       <c r="C3">
-        <v>81896.03408341862</v>
+        <v>53939.28050941755</v>
       </c>
       <c r="D3">
-        <v>6.832108638619173</v>
+        <v>7.900144351751506</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -416,13 +416,13 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>43.01963532551069</v>
+        <v>95.51845307556377</v>
       </c>
       <c r="C4">
-        <v>883.0636615745001</v>
+        <v>1276.414575312263</v>
       </c>
       <c r="D4">
-        <v>4.871634650757432</v>
+        <v>7.483340830090105</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -430,13 +430,13 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>3833.21048095657</v>
+        <v>4855.583327817173</v>
       </c>
       <c r="C5">
-        <v>86351.7602835304</v>
+        <v>99466.18032506436</v>
       </c>
       <c r="D5">
-        <v>4.439064668016577</v>
+        <v>4.881642495920415</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -444,13 +444,13 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>1479.458292819475</v>
+        <v>832.9090224620084</v>
       </c>
       <c r="C6">
-        <v>23660.11065987919</v>
+        <v>22537.39773835019</v>
       </c>
       <c r="D6">
-        <v>6.252964384178536</v>
+        <v>3.695675215620434</v>
       </c>
     </row>
   </sheetData>

--- a/data/gold/results/01_eriksen_replication/table_s5_dk.xlsx
+++ b/data/gold/results/01_eriksen_replication/table_s5_dk.xlsx
@@ -388,13 +388,13 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>4608.260597065414</v>
+        <v>4629.139016586378</v>
       </c>
       <c r="C2">
         <v>76453.5848395347</v>
       </c>
       <c r="D2">
-        <v>6.027527167937912</v>
+        <v>6.054835788671373</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -444,13 +444,13 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>832.9090224620084</v>
+        <v>259.4180916719396</v>
       </c>
       <c r="C6">
-        <v>22537.39773835019</v>
+        <v>10587.34124489906</v>
       </c>
       <c r="D6">
-        <v>3.695675215620434</v>
+        <v>2.450266650250139</v>
       </c>
     </row>
   </sheetData>

--- a/data/gold/results/01_eriksen_replication/table_s5_dk.xlsx
+++ b/data/gold/results/01_eriksen_replication/table_s5_dk.xlsx
@@ -388,13 +388,13 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>4629.139016586378</v>
+        <v>4714.915864429138</v>
       </c>
       <c r="C2">
-        <v>76453.5848395347</v>
+        <v>77531.86853792774</v>
       </c>
       <c r="D2">
-        <v>6.054835788671373</v>
+        <v>6.081261748673906</v>
       </c>
     </row>
     <row r="3" spans="1:4">

--- a/data/gold/results/01_eriksen_replication/table_s5_dk.xlsx
+++ b/data/gold/results/01_eriksen_replication/table_s5_dk.xlsx
@@ -388,13 +388,13 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>4714.915864429138</v>
+        <v>4713.367605953854</v>
       </c>
       <c r="C2">
-        <v>77531.86853792774</v>
+        <v>77477.50333386465</v>
       </c>
       <c r="D2">
-        <v>6.081261748673906</v>
+        <v>6.083530577441423</v>
       </c>
     </row>
     <row r="3" spans="1:4">

--- a/data/gold/results/01_eriksen_replication/table_s5_dk.xlsx
+++ b/data/gold/results/01_eriksen_replication/table_s5_dk.xlsx
@@ -402,13 +402,13 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>4261.281022540152</v>
+        <v>4259.384222540152</v>
       </c>
       <c r="C3">
         <v>53939.28050941755</v>
       </c>
       <c r="D3">
-        <v>7.900144351751506</v>
+        <v>7.896627805030665</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -416,13 +416,13 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>95.51845307556377</v>
+        <v>95.50495307556376</v>
       </c>
       <c r="C4">
         <v>1276.414575312263</v>
       </c>
       <c r="D4">
-        <v>7.483340830090105</v>
+        <v>7.482283179992627</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -430,13 +430,13 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>4855.583327817173</v>
+        <v>4855.460127817173</v>
       </c>
       <c r="C5">
         <v>99466.18032506436</v>
       </c>
       <c r="D5">
-        <v>4.881642495920415</v>
+        <v>4.881518634724984</v>
       </c>
     </row>
     <row r="6" spans="1:4">
